--- a/academias/Física - Estadisticos 20231.xlsx
+++ b/academias/Física - Estadisticos 20231.xlsx
@@ -726,13 +726,13 @@
         <v>22</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -744,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -793,13 +793,13 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -933,28 +933,28 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E14">
         <v>12</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
         <v>7.6</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -965,28 +965,28 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E15">
         <v>99</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
         <v>7.2</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -994,28 +994,28 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E16">
         <v>164</v>
       </c>
       <c r="F16">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G16" s="1">
-        <v>53.8</v>
+        <v>54.5</v>
       </c>
       <c r="H16" s="1">
-        <v>46.2</v>
+        <v>45.5</v>
       </c>
       <c r="I16" s="2">
         <v>4.8</v>
       </c>
       <c r="J16">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K16" s="1">
-        <v>43.6</v>
+        <v>42.9</v>
       </c>
     </row>
   </sheetData>
@@ -1287,13 +1287,13 @@
         <v>22</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1354,13 +1354,13 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1494,13 +1494,13 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -1526,13 +1526,13 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1544,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -1555,13 +1555,13 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1573,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -1848,13 +1848,13 @@
         <v>22</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1915,13 +1915,13 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -2055,28 +2055,28 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E14">
         <v>12</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
         <v>7.6</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2087,28 +2087,28 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E15">
         <v>99</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
         <v>7.2</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2116,28 +2116,28 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E16">
         <v>164</v>
       </c>
       <c r="F16">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G16" s="1">
-        <v>53.8</v>
+        <v>54.5</v>
       </c>
       <c r="H16" s="1">
-        <v>46.2</v>
+        <v>45.5</v>
       </c>
       <c r="I16" s="2">
         <v>4.8</v>
       </c>
       <c r="J16">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K16" s="1">
-        <v>43.6</v>
+        <v>42.9</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Física - Estadisticos 20231.xlsx
+++ b/academias/Física - Estadisticos 20231.xlsx
@@ -659,25 +659,25 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -694,25 +694,25 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -729,25 +729,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>16.1</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -761,28 +761,28 @@
         <v>23</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>30.6</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -793,28 +793,28 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="F10">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>16.9</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J10">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -994,28 +994,28 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E16">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="F16">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1">
-        <v>54.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>45.5</v>
+        <v>9.9</v>
       </c>
       <c r="I16" s="2">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1118,25 +1118,25 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>25.9</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1153,25 +1153,25 @@
         <v>16</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>56.2</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>43.8</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1185,25 +1185,25 @@
         <v>73</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>39.7</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>60.3</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J5">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1322,13 +1322,13 @@
         <v>23</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1354,13 +1354,13 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1462,25 +1462,25 @@
         <v>26</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>61.5</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>38.5</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="J13">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1529,25 +1529,25 @@
         <v>99</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>83.8</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="J15">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1555,28 +1555,28 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F16">
-        <v>301</v>
+        <v>257</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J16">
-        <v>301</v>
+        <v>233</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>77.2</v>
       </c>
     </row>
   </sheetData>
@@ -1679,19 +1679,19 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>88.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>11.1</v>
+        <v>25.9</v>
       </c>
       <c r="I3" s="2">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1714,19 +1714,19 @@
         <v>16</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>81.2</v>
+        <v>56.2</v>
       </c>
       <c r="H4" s="1">
-        <v>18.8</v>
+        <v>43.8</v>
       </c>
       <c r="I4" s="2">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1746,19 +1746,19 @@
         <v>73</v>
       </c>
       <c r="E5">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1">
-        <v>89</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>11</v>
+        <v>21.9</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1781,25 +1781,25 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1816,25 +1816,25 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1851,25 +1851,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>16.1</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1883,28 +1883,28 @@
         <v>23</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>30.6</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J9">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1915,28 +1915,28 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="F10">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>16.9</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2023,19 +2023,19 @@
         <v>26</v>
       </c>
       <c r="E13">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>100</v>
+        <v>61.5</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="I13" s="2">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2090,19 +2090,19 @@
         <v>99</v>
       </c>
       <c r="E15">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1">
-        <v>100</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="I15" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2116,28 +2116,28 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E16">
-        <v>164</v>
+        <v>254</v>
       </c>
       <c r="F16">
-        <v>137</v>
+        <v>48</v>
       </c>
       <c r="G16" s="1">
-        <v>54.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>45.5</v>
+        <v>15.9</v>
       </c>
       <c r="I16" s="2">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="J16">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Física - Estadisticos 20231.xlsx
+++ b/academias/Física - Estadisticos 20231.xlsx
@@ -1220,25 +1220,25 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1255,25 +1255,25 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1290,25 +1290,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>90.3</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1325,25 +1325,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1357,25 +1357,25 @@
         <v>130</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="F10">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>14.6</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1392,25 +1392,25 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J11">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1427,25 +1427,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>75.8</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>24.2</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1497,25 +1497,25 @@
         <v>12</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F14">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1529,25 +1529,25 @@
         <v>99</v>
       </c>
       <c r="E15">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="F15">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="G15" s="1">
-        <v>16.2</v>
+        <v>77.8</v>
       </c>
       <c r="H15" s="1">
-        <v>83.8</v>
+        <v>22.2</v>
       </c>
       <c r="I15" s="2">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J15">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="K15" s="1">
-        <v>73.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1558,25 +1558,25 @@
         <v>302</v>
       </c>
       <c r="E16">
-        <v>45</v>
+        <v>217</v>
       </c>
       <c r="F16">
-        <v>257</v>
+        <v>85</v>
       </c>
       <c r="G16" s="1">
-        <v>14.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>85.09999999999999</v>
+        <v>28.1</v>
       </c>
       <c r="I16" s="2">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="J16">
-        <v>233</v>
+        <v>33</v>
       </c>
       <c r="K16" s="1">
-        <v>77.2</v>
+        <v>10.9</v>
       </c>
     </row>
   </sheetData>
@@ -1793,7 +1793,7 @@
         <v>5.3</v>
       </c>
       <c r="I6" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1816,19 +1816,19 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H7" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1851,19 +1851,19 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>83.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="H8" s="1">
-        <v>16.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I8" s="2">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1886,19 +1886,19 @@
         <v>36</v>
       </c>
       <c r="E9">
+        <v>27</v>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9" s="1">
+        <v>75</v>
+      </c>
+      <c r="H9" s="1">
         <v>25</v>
       </c>
-      <c r="F9">
-        <v>11</v>
-      </c>
-      <c r="G9" s="1">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="H9" s="1">
-        <v>30.6</v>
-      </c>
       <c r="I9" s="2">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1918,19 +1918,19 @@
         <v>130</v>
       </c>
       <c r="E10">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1">
-        <v>83.09999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>16.9</v>
+        <v>14.6</v>
       </c>
       <c r="I10" s="2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1988,19 +1988,19 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>100</v>
+        <v>84.8</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="I12" s="2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2058,19 +2058,19 @@
         <v>12</v>
       </c>
       <c r="E14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I14" s="2">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2090,19 +2090,19 @@
         <v>99</v>
       </c>
       <c r="E15">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G15" s="1">
-        <v>89.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="H15" s="1">
-        <v>10.1</v>
+        <v>19.2</v>
       </c>
       <c r="I15" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2119,19 +2119,19 @@
         <v>302</v>
       </c>
       <c r="E16">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="F16">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G16" s="1">
-        <v>84.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>15.9</v>
+        <v>17.9</v>
       </c>
       <c r="I16" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J16">
         <v>0</v>

--- a/academias/Física - Estadisticos 20231.xlsx
+++ b/academias/Física - Estadisticos 20231.xlsx
@@ -1427,25 +1427,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>75.8</v>
+        <v>81.8</v>
       </c>
       <c r="H12" s="1">
-        <v>24.2</v>
+        <v>18.2</v>
       </c>
       <c r="I12" s="2">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1529,25 +1529,25 @@
         <v>99</v>
       </c>
       <c r="E15">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F15">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G15" s="1">
-        <v>77.8</v>
+        <v>79.8</v>
       </c>
       <c r="H15" s="1">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="I15" s="2">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1558,25 +1558,25 @@
         <v>302</v>
       </c>
       <c r="E16">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F16">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G16" s="1">
-        <v>71.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="H16" s="1">
-        <v>28.1</v>
+        <v>27.5</v>
       </c>
       <c r="I16" s="2">
         <v>6.2</v>
       </c>
       <c r="J16">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K16" s="1">
-        <v>10.9</v>
+        <v>9.9</v>
       </c>
     </row>
   </sheetData>
@@ -1988,19 +1988,19 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>84.8</v>
+        <v>81.8</v>
       </c>
       <c r="H12" s="1">
-        <v>15.2</v>
+        <v>18.2</v>
       </c>
       <c r="I12" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2090,19 +2090,19 @@
         <v>99</v>
       </c>
       <c r="E15">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G15" s="1">
-        <v>80.8</v>
+        <v>79.8</v>
       </c>
       <c r="H15" s="1">
-        <v>19.2</v>
+        <v>20.2</v>
       </c>
       <c r="I15" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2119,19 +2119,19 @@
         <v>302</v>
       </c>
       <c r="E16">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F16">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G16" s="1">
-        <v>82.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="H16" s="1">
-        <v>17.9</v>
+        <v>18.2</v>
       </c>
       <c r="I16" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J16">
         <v>0</v>

--- a/academias/Física - Estadisticos 20231.xlsx
+++ b/academias/Física - Estadisticos 20231.xlsx
@@ -933,28 +933,28 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14">
         <v>12</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="I14" s="2">
         <v>7.6</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -965,28 +965,28 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>99</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2">
         <v>7.2</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -994,28 +994,28 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E16">
         <v>272</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G16" s="1">
-        <v>90.09999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="H16" s="1">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="I16" s="2">
         <v>7.4</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -1083,25 +1083,25 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>23.3</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1185,25 +1185,25 @@
         <v>73</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="F5">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="G5" s="1">
-        <v>39.7</v>
+        <v>71.2</v>
       </c>
       <c r="H5" s="1">
-        <v>60.3</v>
+        <v>28.8</v>
       </c>
       <c r="I5" s="2">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K5" s="1">
-        <v>41.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1494,28 +1494,28 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14">
         <v>8</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>66.7</v>
+        <v>61.5</v>
       </c>
       <c r="H14" s="1">
-        <v>33.3</v>
+        <v>38.5</v>
       </c>
       <c r="I14" s="2">
         <v>6</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1526,28 +1526,28 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>79</v>
       </c>
       <c r="F15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15" s="1">
-        <v>79.8</v>
+        <v>79</v>
       </c>
       <c r="H15" s="1">
-        <v>20.2</v>
+        <v>21</v>
       </c>
       <c r="I15" s="2">
         <v>6</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1555,28 +1555,28 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E16">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="F16">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="G16" s="1">
-        <v>72.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>27.5</v>
+        <v>20.1</v>
       </c>
       <c r="I16" s="2">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="J16">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="K16" s="1">
-        <v>9.9</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1644,19 +1644,19 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>93.3</v>
+        <v>83.3</v>
       </c>
       <c r="H2" s="1">
-        <v>6.7</v>
+        <v>16.7</v>
       </c>
       <c r="I2" s="2">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1746,19 +1746,19 @@
         <v>73</v>
       </c>
       <c r="E5">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1">
-        <v>78.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="H5" s="1">
-        <v>21.9</v>
+        <v>26</v>
       </c>
       <c r="I5" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2055,28 +2055,28 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14">
         <v>8</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>66.7</v>
+        <v>61.5</v>
       </c>
       <c r="H14" s="1">
-        <v>33.3</v>
+        <v>38.5</v>
       </c>
       <c r="I14" s="2">
         <v>6.9</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2087,28 +2087,28 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>79</v>
       </c>
       <c r="F15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15" s="1">
-        <v>79.8</v>
+        <v>79</v>
       </c>
       <c r="H15" s="1">
-        <v>20.2</v>
+        <v>21</v>
       </c>
       <c r="I15" s="2">
         <v>6.7</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2116,28 +2116,28 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E16">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F16">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G16" s="1">
-        <v>81.8</v>
+        <v>80.5</v>
       </c>
       <c r="H16" s="1">
-        <v>18.2</v>
+        <v>19.5</v>
       </c>
       <c r="I16" s="2">
         <v>7.2</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Física - Estadisticos 20231.xlsx
+++ b/academias/Física - Estadisticos 20231.xlsx
@@ -1083,25 +1083,25 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>76.7</v>
+        <v>83.3</v>
       </c>
       <c r="H2" s="1">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="I2" s="2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1185,25 +1185,25 @@
         <v>73</v>
       </c>
       <c r="E5">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1">
-        <v>71.2</v>
+        <v>74</v>
       </c>
       <c r="H5" s="1">
-        <v>28.8</v>
+        <v>26</v>
       </c>
       <c r="I5" s="2">
         <v>6.1</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1462,19 +1462,19 @@
         <v>26</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>61.5</v>
+        <v>69.2</v>
       </c>
       <c r="H13" s="1">
-        <v>38.5</v>
+        <v>30.8</v>
       </c>
       <c r="I13" s="2">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1529,19 +1529,19 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F15">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G15" s="1">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H15" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I15" s="2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1558,25 +1558,25 @@
         <v>303</v>
       </c>
       <c r="E16">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F16">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G16" s="1">
-        <v>79.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="H16" s="1">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="I16" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -1644,16 +1644,16 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>83.3</v>
+        <v>93.3</v>
       </c>
       <c r="H2" s="1">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
       <c r="I2" s="2">
         <v>7.3</v>
@@ -1679,19 +1679,19 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>74.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="H3" s="1">
-        <v>25.9</v>
+        <v>3.7</v>
       </c>
       <c r="I3" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1714,16 +1714,16 @@
         <v>16</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>56.2</v>
+        <v>81.2</v>
       </c>
       <c r="H4" s="1">
-        <v>43.8</v>
+        <v>18.8</v>
       </c>
       <c r="I4" s="2">
         <v>7.1</v>
@@ -1746,19 +1746,19 @@
         <v>73</v>
       </c>
       <c r="E5">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>74</v>
+        <v>91.8</v>
       </c>
       <c r="H5" s="1">
-        <v>26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1781,19 +1781,19 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1816,19 +1816,19 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="H7" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I7" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1851,16 +1851,16 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>90.3</v>
+        <v>96.8</v>
       </c>
       <c r="H8" s="1">
-        <v>9.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="I8" s="2">
         <v>7.7</v>
@@ -1886,19 +1886,19 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1918,19 +1918,19 @@
         <v>130</v>
       </c>
       <c r="E10">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>85.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="H10" s="1">
-        <v>14.6</v>
+        <v>1.5</v>
       </c>
       <c r="I10" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2023,19 +2023,19 @@
         <v>26</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>61.5</v>
+        <v>69.2</v>
       </c>
       <c r="H13" s="1">
-        <v>38.5</v>
+        <v>30.8</v>
       </c>
       <c r="I13" s="2">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2090,19 +2090,19 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F15">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G15" s="1">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H15" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I15" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2119,19 +2119,19 @@
         <v>303</v>
       </c>
       <c r="E16">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="F16">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="G16" s="1">
-        <v>80.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>19.5</v>
+        <v>8.9</v>
       </c>
       <c r="I16" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J16">
         <v>1</v>

--- a/academias/Física - Estadisticos 20231.xlsx
+++ b/academias/Física - Estadisticos 20231.xlsx
@@ -936,25 +936,25 @@
         <v>13</v>
       </c>
       <c r="E14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -968,25 +968,25 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
         <v>7.2</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -997,25 +997,25 @@
         <v>303</v>
       </c>
       <c r="E16">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F16">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1">
-        <v>89.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="I16" s="2">
         <v>7.4</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1497,25 +1497,25 @@
         <v>13</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>61.5</v>
+        <v>69.2</v>
       </c>
       <c r="H14" s="1">
-        <v>38.5</v>
+        <v>30.8</v>
       </c>
       <c r="I14" s="2">
         <v>6</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1529,25 +1529,25 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G15" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H15" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I15" s="2">
         <v>6.2</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1558,25 +1558,25 @@
         <v>303</v>
       </c>
       <c r="E16">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F16">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G16" s="1">
-        <v>81.2</v>
+        <v>81.5</v>
       </c>
       <c r="H16" s="1">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="I16" s="2">
         <v>6.8</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1953,19 +1953,19 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I11" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1988,19 +1988,19 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>81.8</v>
+        <v>97</v>
       </c>
       <c r="H12" s="1">
-        <v>18.2</v>
+        <v>3</v>
       </c>
       <c r="I12" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2023,19 +2023,19 @@
         <v>26</v>
       </c>
       <c r="E13">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>69.2</v>
+        <v>96.2</v>
       </c>
       <c r="H13" s="1">
-        <v>30.8</v>
+        <v>3.8</v>
       </c>
       <c r="I13" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2058,25 +2058,25 @@
         <v>13</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>61.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>38.5</v>
+        <v>15.4</v>
       </c>
       <c r="I14" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2090,25 +2090,25 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="H15" s="1">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I15" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2119,25 +2119,25 @@
         <v>303</v>
       </c>
       <c r="E16">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="F16">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G16" s="1">
-        <v>91.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="H16" s="1">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="I16" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Física - Estadisticos 20231.xlsx
+++ b/academias/Física - Estadisticos 20231.xlsx
@@ -1851,19 +1851,19 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1918,16 +1918,16 @@
         <v>130</v>
       </c>
       <c r="E10">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>98.5</v>
+        <v>99.2</v>
       </c>
       <c r="H10" s="1">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="I10" s="2">
         <v>7.9</v>
@@ -2119,16 +2119,16 @@
         <v>303</v>
       </c>
       <c r="E16">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1">
-        <v>95.7</v>
+        <v>96</v>
       </c>
       <c r="H16" s="1">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I16" s="2">
         <v>7.4</v>

--- a/academias/Física - Estadisticos 20231.xlsx
+++ b/academias/Física - Estadisticos 20231.xlsx
@@ -1656,7 +1656,7 @@
         <v>6.7</v>
       </c>
       <c r="I2" s="2">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1691,7 +1691,7 @@
         <v>3.7</v>
       </c>
       <c r="I3" s="2">
-        <v>7.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>18.8</v>
       </c>
       <c r="I4" s="2">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1758,7 +1758,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>7.3</v>
+        <v>9.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1828,7 +1828,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0.8</v>
       </c>
       <c r="I10" s="2">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>3.6</v>
       </c>
       <c r="I11" s="2">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="2">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         <v>3.8</v>
       </c>
       <c r="I13" s="2">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2070,7 +2070,7 @@
         <v>15.4</v>
       </c>
       <c r="I14" s="2">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>5</v>
       </c>
       <c r="I15" s="2">
-        <v>6.9</v>
+        <v>9.6</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>4</v>
       </c>
       <c r="I16" s="2">
-        <v>7.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J16">
         <v>0</v>

--- a/academias/Física - Estadisticos 20231.xlsx
+++ b/academias/Física - Estadisticos 20231.xlsx
@@ -1656,7 +1656,7 @@
         <v>6.7</v>
       </c>
       <c r="I2" s="2">
-        <v>9.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1691,7 +1691,7 @@
         <v>3.7</v>
       </c>
       <c r="I3" s="2">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>18.8</v>
       </c>
       <c r="I4" s="2">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1758,7 +1758,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1828,7 +1828,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="2">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0.8</v>
       </c>
       <c r="I10" s="2">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>3.6</v>
       </c>
       <c r="I11" s="2">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="2">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         <v>3.8</v>
       </c>
       <c r="I13" s="2">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2070,7 +2070,7 @@
         <v>15.4</v>
       </c>
       <c r="I14" s="2">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>5</v>
       </c>
       <c r="I15" s="2">
-        <v>9.6</v>
+        <v>6.9</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>4</v>
       </c>
       <c r="I16" s="2">
-        <v>9.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
         <v>0</v>
